--- a/data/processed/positivacao/2025-11_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2025-11_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -27129,7 +27129,7 @@
     <row r="1031">
       <c r="A1031" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B1031" t="inlineStr"/>
@@ -38091,7 +38091,7 @@
     <row r="1453">
       <c r="A1453" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1453" t="inlineStr"/>
@@ -66333,7 +66333,7 @@
     <row r="2540">
       <c r="A2540" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2540" t="inlineStr"/>
@@ -67926,12 +67926,12 @@
       <c r="A2602" t="inlineStr"/>
       <c r="B2602" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 9 cliente(s), não positivou 85 cliente(s) - Total vendido: R$ 15.674,27
+          <t>Vendedor 1 - VENDEDOR 01: positivou 9 cliente(s), não positivou 85 cliente(s) - Total vendido: R$ 15.674,27
 Vendedor 18 - LOJA: positivou 280 cliente(s), não positivou 647 cliente(s) - Total vendido: R$ 87.619,59
-Vendedor 3 - FERNANDA: positivou 109 cliente(s), não positivou 312 cliente(s) - Total vendido: R$ 134.085,13
-Vendedor 4 - DANIELA: positivou 135 cliente(s), não positivou 505 cliente(s) - Total vendido: R$ 75.027,84
+Vendedor 3 - VENDEDOR 03: positivou 109 cliente(s), não positivou 312 cliente(s) - Total vendido: R$ 134.085,13
+Vendedor 4 - VENDEDOR 04: positivou 135 cliente(s), não positivou 505 cliente(s) - Total vendido: R$ 75.027,84
 Vendedor 5 - SITE: positivou 1 cliente(s), não positivou 444 cliente(s) - Total vendido: R$ 21,83
-Vendedor 8 - RAFAEL: positivou 0 cliente(s), não positivou 60 cliente(s) - Total vendido: R$ 0,00</t>
+Vendedor 8 - VENDEDOR 08: positivou 0 cliente(s), não positivou 60 cliente(s) - Total vendido: R$ 0,00</t>
         </is>
       </c>
       <c r="C2602" t="inlineStr"/>
